--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484043_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484043_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1458</v>
+        <v>2.2656</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0311</v>
+        <v>0.3192</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1147</v>
+        <v>1.9463</v>
       </c>
       <c r="G2" t="n">
         <v>-2.1373</v>
@@ -610,13 +610,13 @@
         <v>2.9758</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3624</v>
+        <v>1.4823</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7209</v>
+        <v>1.0091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6415</v>
+        <v>0.4732</v>
       </c>
       <c r="V2" t="n">
         <v>1.1352</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2172</v>
+        <v>1.2829</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5425</v>
+        <v>2.1808</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7598</v>
+        <v>-0.8979</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7793</v>
+        <v>1.5857</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.3405</v>
+        <v>0.5998</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5612</v>
+        <v>0.9859</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1447</v>
+        <v>2.5152</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.5504</v>
+        <v>1.2702</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4057</v>
+        <v>1.245</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6346</v>
+        <v>-0.9295</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7901</v>
+        <v>-0.6704</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1555</v>
+        <v>-0.2591</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0.5952</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1741</v>
+        <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8018</v>
+        <v>-0.2947</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9784</v>
+        <v>-0.3344</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8234</v>
+        <v>0.0396</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1947</v>
+        <v>-0.6032</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>-0.6032</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1808</v>
+        <v>0.7191</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0788</v>
+        <v>1.2418</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8979</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5857</v>
+        <v>-1.9038</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5998</v>
+        <v>-0.7765</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9859</v>
+        <v>-1.1273</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5152</v>
+        <v>-0.1972</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2702</v>
+        <v>0.1464</v>
       </c>
       <c r="L4" t="n">
-        <v>1.245</v>
+        <v>-0.3436</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9295</v>
+        <v>-1.7067</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6704</v>
+        <v>-0.923</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2591</v>
+        <v>-0.7837</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5952</v>
+        <v>2.1822</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5952</v>
+        <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3968</v>
+        <v>0.4407</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4364</v>
+        <v>0.4309</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0396</v>
+        <v>0.0098</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6032</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2765</v>
+        <v>0.0295</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4426</v>
+        <v>-1.4778</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7191</v>
+        <v>1.5073</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9038</v>
+        <v>-1.7793</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7765</v>
+        <v>-3.3405</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1273</v>
+        <v>1.5612</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1972</v>
+        <v>-0.1447</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1464</v>
+        <v>-1.5504</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3436</v>
+        <v>1.4057</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7067</v>
+        <v>-1.6346</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.923</v>
+        <v>-1.7901</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7837</v>
+        <v>0.1555</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1822</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1984</v>
+        <v>-3.1741</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3806</v>
+        <v>3.1741</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5548999999999999</v>
+        <v>1.614</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3683</v>
+        <v>1.0431</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1865</v>
+        <v>0.5709</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2065</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SANTANDREU RODRIGUEZ</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5423</v>
+        <v>-0.3725</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.773</v>
+        <v>0.0372</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2307</v>
+        <v>-0.4097</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9671999999999999</v>
+        <v>-0.7863</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5189</v>
+        <v>-0.7863</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4483</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0805</v>
+        <v>0.0202</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0403</v>
+        <v>0.0202</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8867</v>
+        <v>-0.8065</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4786</v>
+        <v>-0.8065</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4081</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0414</v>
+        <v>0.017</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.187</v>
+        <v>0.017</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1456</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>M. SANTANDREU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5766</v>
+        <v>-0.4059</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1669</v>
+        <v>-1.6086</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4097</v>
+        <v>1.2027</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7863</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7863</v>
+        <v>0.5189</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.4483</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0202</v>
+        <v>0.0805</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0202</v>
+        <v>0.0403</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8065</v>
+        <v>0.8867</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8065</v>
+        <v>0.4786</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.4081</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.187</v>
+        <v>0.0949</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.187</v>
+        <v>-0.0227</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3292</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4313</v>
+        <v>-0.3285</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8979</v>
+        <v>-0.2436</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5276</v>
+        <v>-0.2045</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.771</v>
+        <v>-0.1061</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.0984</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0051</v>
+        <v>0.584</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.035</v>
+        <v>0.4234</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>0.1606</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5327</v>
+        <v>-0.7886</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.736</v>
+        <v>-0.5295</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7967</v>
+        <v>-0.2591</v>
       </c>
       <c r="P8" t="n">
         <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3968</v>
+        <v>0.2437</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4364</v>
+        <v>0.2778</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0396</v>
+        <v>-0.034</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3487</v>
+        <v>-1.2272</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.105</v>
+        <v>-0.3292</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2436</v>
+        <v>-0.8979</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2045</v>
+        <v>-1.5276</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1061</v>
+        <v>-0.771</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0984</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.584</v>
+        <v>0.0051</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4234</v>
+        <v>-0.035</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1606</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7886</v>
+        <v>-1.5327</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5295</v>
+        <v>-0.736</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2591</v>
+        <v>-0.7967</v>
       </c>
       <c r="P9" t="n">
         <v>0.5952</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.2947</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4988</v>
+        <v>-0.3344</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.034</v>
+        <v>0.0396</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8483</v>
+        <v>-1.7463</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9536</v>
+        <v>-0.8516</v>
       </c>
       <c r="F10" t="n">
         <v>-0.8947000000000001</v>
@@ -1234,10 +1234,10 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3344</v>
+        <v>-0.2324</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3741</v>
+        <v>-0.272</v>
       </c>
       <c r="U10" t="n">
         <v>0.0396</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.128</v>
+        <v>-2.7683</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7465</v>
+        <v>-1.7363</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3815</v>
+        <v>-1.032</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0804</v>
+        <v>-5.9564</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6838</v>
+        <v>-2.8224</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3966</v>
+        <v>-3.134</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1591</v>
+        <v>-2.6926</v>
       </c>
       <c r="K11" t="n">
-        <v>0.121</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2801</v>
+        <v>-2.0782</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9213</v>
+        <v>-3.2638</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8048</v>
+        <v>-2.208</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1165</v>
+        <v>-1.0558</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0476</v>
+        <v>-0.2961</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8615</v>
+        <v>-0.4647</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8138</v>
+        <v>0.1686</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>3.0874</v>
       </c>
       <c r="W11" t="n">
-        <v>0.266</v>
+        <v>2.4129</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2413</v>
+        <v>-2.78</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9007</v>
+        <v>-2.174</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3406</v>
+        <v>-0.606</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.9564</v>
+        <v>-3.0804</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8224</v>
+        <v>-1.6838</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.134</v>
+        <v>-1.3966</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6926</v>
+        <v>-1.1591</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6143999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0782</v>
+        <v>-1.2801</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2638</v>
+        <v>-1.9213</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.208</v>
+        <v>-1.8048</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0558</v>
+        <v>-0.1165</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7691</v>
+        <v>0.3004</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6291</v>
+        <v>-0.289</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.14</v>
+        <v>0.5894</v>
       </c>
       <c r="V12" t="n">
-        <v>3.0874</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4129</v>
+        <v>0.266</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4736</v>
+        <v>-3.7101</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5063</v>
+        <v>-2.9112</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9673</v>
+        <v>-0.799</v>
       </c>
       <c r="G13" t="n">
         <v>-3.5421</v>
@@ -1468,13 +1468,13 @@
         <v>2.9758</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0443</v>
+        <v>0.8078</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1245</v>
+        <v>0.4706</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1688</v>
+        <v>0.3372</v>
       </c>
       <c r="V13" t="n">
         <v>1.2065</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.2207</v>
+        <v>-9.285300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.5733</v>
+        <v>-7.638199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6471</v>
+        <v>-1.6472</v>
       </c>
       <c r="G14" t="n">
         <v>-20.2755</v>
@@ -1516,7 +1516,7 @@
         <v>-11.4654</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.81</v>
+        <v>-8.809999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>-2.431</v>
@@ -1546,13 +1546,13 @@
         <v>17.8548</v>
       </c>
       <c r="S14" t="n">
-        <v>2.947700000000001</v>
+        <v>3.8829</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5962000000000001</v>
+        <v>1.5313</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3514</v>
+        <v>2.351500000000001</v>
       </c>
       <c r="V14" t="n">
         <v>3.139600000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6741</v>
+        <v>6.1699</v>
       </c>
       <c r="E15" t="n">
-        <v>3.153</v>
+        <v>2.5408</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5211</v>
+        <v>3.6291</v>
       </c>
       <c r="G15" t="n">
         <v>5.0884</v>
@@ -1624,13 +1624,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6784</v>
+        <v>0.1742</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6236</v>
+        <v>0.0114</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0548</v>
+        <v>0.1628</v>
       </c>
       <c r="V15" t="n">
         <v>2.0976</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1789</v>
+        <v>5.3609</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2386</v>
+        <v>3.3406</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9404</v>
+        <v>2.0203</v>
       </c>
       <c r="G16" t="n">
         <v>6.5199</v>
@@ -1702,13 +1702,13 @@
         <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6497000000000001</v>
+        <v>-0.4677</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.493</v>
+        <v>-0.391</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1566</v>
+        <v>-0.0767</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2945</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7041</v>
+        <v>2.9319</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4133</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2907</v>
+        <v>2.3145</v>
       </c>
       <c r="G17" t="n">
         <v>2.0645</v>
@@ -1780,13 +1780,13 @@
         <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4546</v>
+        <v>-0.2268</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8728</v>
+        <v>-0.6688</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4182</v>
+        <v>0.442</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2945</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5351</v>
+        <v>2.1864</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7406</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7945</v>
+        <v>1.5478</v>
       </c>
       <c r="G18" t="n">
         <v>2.7444</v>
@@ -1858,13 +1858,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1925</v>
+        <v>-0.5413</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4307</v>
+        <v>-0.5327</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7619</v>
+        <v>-0.0086</v>
       </c>
       <c r="V18" t="n">
         <v>0.38</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9236</v>
+        <v>0.1814</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7892</v>
+        <v>0.075</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1344</v>
+        <v>0.1064</v>
       </c>
       <c r="G19" t="n">
         <v>1.6953</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7125</v>
+        <v>-0.0298</v>
       </c>
       <c r="T19" t="n">
-        <v>0.924</v>
+        <v>0.2098</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2115</v>
+        <v>-0.2395</v>
       </c>
       <c r="V19" t="n">
         <v>-1.881</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0062</v>
+        <v>0.1745</v>
       </c>
       <c r="E20" t="n">
         <v>-2.613</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6193</v>
+        <v>2.7876</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5716</v>
@@ -2014,13 +2014,13 @@
         <v>2.1822</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3809</v>
+        <v>-0.2126</v>
       </c>
       <c r="T20" t="n">
         <v>0.2551</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6361</v>
+        <v>-0.4677</v>
       </c>
       <c r="V20" t="n">
         <v>1.7603</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1654</v>
+        <v>-0.3847</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5613</v>
+        <v>-0.0512</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3959</v>
+        <v>-0.3335</v>
       </c>
       <c r="G21" t="n">
         <v>1.3628</v>
@@ -2092,13 +2092,13 @@
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2221</v>
+        <v>0.0028</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5498</v>
+        <v>-0.0396</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7718</v>
+        <v>0.0424</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1469</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>M. BERNADÍ VALLS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7914</v>
+        <v>-0.519</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7446</v>
+        <v>0.2365</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0469</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6854</v>
+        <v>1.3856</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0454</v>
+        <v>0.1613</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.64</v>
+        <v>1.2244</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6199</v>
+        <v>1.4187</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0202</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.64</v>
+        <v>0.8032</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.033</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.4542</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.4211</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.106</v>
+        <v>-0.4648</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1247</v>
+        <v>-0.7935</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0187</v>
+        <v>0.3287</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.0431</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.6463</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. BERNADÍ VALLS</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-0.6614</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0325</v>
+        <v>-0.6425</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0038</v>
+        <v>-0.0188</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3856</v>
+        <v>-0.6854</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1613</v>
+        <v>-0.0454</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2244</v>
+        <v>-0.64</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4187</v>
+        <v>-0.6199</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8032</v>
+        <v>-0.64</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.033</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4542</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4211</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9171</v>
+        <v>0.0241</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.0227</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0804</v>
+        <v>0.0468</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0431</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.6463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8733</v>
+        <v>-4.5392</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8009</v>
+        <v>-2.4948</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0724</v>
+        <v>-2.0444</v>
       </c>
       <c r="G24" t="n">
         <v>1.6718</v>
@@ -2326,13 +2326,13 @@
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8599</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6858</v>
+        <v>-0.3797</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1741</v>
+        <v>-0.146</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7176</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.2206</v>
+        <v>10.9007</v>
       </c>
       <c r="E25" t="n">
-        <v>1.647400000000001</v>
+        <v>1.647399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>8.5732</v>
+        <v>9.253499999999999</v>
       </c>
       <c r="G25" t="n">
         <v>20.2757</v>
@@ -2404,13 +2404,13 @@
         <v>13.887</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.9477</v>
+        <v>-2.2676</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.3516</v>
+        <v>-2.3517</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5962999999999999</v>
+        <v>0.08419999999999991</v>
       </c>
       <c r="V25" t="n">
         <v>-3.1397</v>
